--- a/SuppXLS/Scen_B_SYS_MaxGrowthRates.xlsx
+++ b/SuppXLS/Scen_B_SYS_MaxGrowthRates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\TIM 2100\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1098FE90-3470-47F8-A549-422EFCC25A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41277C3F-1897-40D4-B67F-BC76DE1EEB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{39DC52AD-7AD8-48BE-9D85-AA1C40791A2D}"/>
+    <workbookView xWindow="3550" yWindow="14290" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{39DC52AD-7AD8-48BE-9D85-AA1C40791A2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="6" r:id="rId1"/>
@@ -6126,8 +6126,8 @@
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>68792</xdr:rowOff>
     </xdr:to>
@@ -6464,17 +6464,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F13930EE-8DBF-4E65-B94E-3B7AE49D01AA}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="10" width="8.28515625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" customWidth="1"/>
+    <col min="1" max="4" width="21.7265625" customWidth="1"/>
+    <col min="5" max="6" width="14.26953125" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" customWidth="1"/>
+    <col min="8" max="10" width="8.26953125" customWidth="1"/>
+    <col min="11" max="11" width="9.7265625" customWidth="1"/>
+    <col min="12" max="12" width="8.26953125" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -9317,35 +9317,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E206C345-0D8E-4CDB-A3D4-9EEBCC27251E}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.54296875" customWidth="1"/>
+    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30">
@@ -9816,7 +9816,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+    <row r="10" spans="1:30" ht="15" thickBot="1">
       <c r="A10" s="22" t="s">
         <v>56</v>
       </c>
@@ -10075,15 +10075,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89417C8F-9D07-4311-9372-0B0C534E50C4}">
   <dimension ref="A2:N32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="39.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:14">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="H20" s="46"/>
     </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1">
+    <row r="21" spans="1:12" ht="15" thickBot="1">
       <c r="B21" s="47" t="s">
         <v>216</v>
       </c>
@@ -10641,16 +10641,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B92B0C-7472-4C75-A119-CE0EE6C8A8E0}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:Z66"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" customWidth="1"/>
+    <col min="9" max="9" width="16.1796875" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="39.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:26">
@@ -11384,8 +11385,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="63">
-        <f>7-6.7</f>
-        <v>0.29999999999999982</v>
+        <v>2</v>
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
@@ -11556,9 +11556,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10721BC9-19B1-4D97-BFD3-7736E255AD14}">
   <dimension ref="B2:R31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
@@ -12260,20 +12260,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9933FEB4-63EA-406B-A848-C3344FC12632}">
   <dimension ref="A2:N37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.26953125" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="38.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="H35" s="46"/>
     </row>
-    <row r="36" spans="2:8" ht="15.75" thickBot="1">
+    <row r="36" spans="2:8" ht="15" thickBot="1">
       <c r="B36" s="47" t="s">
         <v>216</v>
       </c>
@@ -13097,19 +13097,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5F46D0-BFBE-459D-AD94-C3EBC85EC70F}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A2:N24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13502,7 +13502,7 @@
       <c r="B22" s="45"/>
       <c r="H22" s="46"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1">
+    <row r="23" spans="1:8" ht="15" thickBot="1">
       <c r="B23" s="47" t="s">
         <v>216</v>
       </c>
@@ -13554,19 +13554,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6663777E-BCE4-472D-B253-88326C1C4E47}">
   <dimension ref="A2:N10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.26953125" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="38.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:14">
@@ -13761,22 +13761,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41B7AF2-8905-43A5-8387-D99F068F4BCD}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A2:P68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" customWidth="1"/>
+    <col min="14" max="14" width="13.54296875" customWidth="1"/>
+    <col min="15" max="15" width="10.7265625" customWidth="1"/>
+    <col min="16" max="16" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15">
